--- a/InputFiles/GC/TC01_GC_phs001905_SmpTumSta-NSD_SmpType-Tissue_LibStr_TargetedCapture.xlsx
+++ b/InputFiles/GC/TC01_GC_phs001905_SmpTumSta-NSD_SmpType-Tissue_LibStr_TargetedCapture.xlsx
@@ -536,8 +536,9 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+          <t>MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
 MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p)
+MATCH (f)-[:from_sample]-&gt;(samp)
 WHERE s.phs_accession = "phs001905"
   AND samp.sample_tumor_status = "Not specified in data"
   AND samp.sample_type = "Tissue"
@@ -546,8 +547,7 @@
   count(DISTINCT s) AS Studies,
   count(DISTINCT p) AS Participants,
   count(DISTINCT samp) AS Samples,
-  count(DISTINCT f) AS Files
-</t>
+  count(DISTINCT f) AS Files</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
